--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y289"/>
+  <dimension ref="A1:Y290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23295,6 +23295,85 @@
         <v>256</v>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>200</v>
+      </c>
+      <c r="C290" t="n">
+        <v>95</v>
+      </c>
+      <c r="D290" t="n">
+        <v>100</v>
+      </c>
+      <c r="E290" t="n">
+        <v>95</v>
+      </c>
+      <c r="F290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" t="n">
+        <v>186</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" t="n">
+        <v>186</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="n">
+        <v>200</v>
+      </c>
+      <c r="L290" t="n">
+        <v>0</v>
+      </c>
+      <c r="M290" t="n">
+        <v>186</v>
+      </c>
+      <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>3</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>36</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0</v>
+      </c>
+      <c r="S290" t="n">
+        <v>272</v>
+      </c>
+      <c r="T290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U290" t="n">
+        <v>260</v>
+      </c>
+      <c r="V290" t="n">
+        <v>0</v>
+      </c>
+      <c r="W290" t="n">
+        <v>260</v>
+      </c>
+      <c r="X290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y290"/>
+  <dimension ref="A1:Y291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23374,6 +23374,85 @@
         <v>260</v>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>200</v>
+      </c>
+      <c r="C291" t="n">
+        <v>89</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" t="n">
+        <v>0</v>
+      </c>
+      <c r="F291" t="n">
+        <v>0</v>
+      </c>
+      <c r="G291" t="n">
+        <v>1</v>
+      </c>
+      <c r="H291" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" t="n">
+        <v>1</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
+        <v>1</v>
+      </c>
+      <c r="L291" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" t="n">
+        <v>1</v>
+      </c>
+      <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="P291" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>37</v>
+      </c>
+      <c r="R291" t="n">
+        <v>0</v>
+      </c>
+      <c r="S291" t="n">
+        <v>257</v>
+      </c>
+      <c r="T291" t="n">
+        <v>0</v>
+      </c>
+      <c r="U291" t="n">
+        <v>257</v>
+      </c>
+      <c r="V291" t="n">
+        <v>0</v>
+      </c>
+      <c r="W291" t="n">
+        <v>257</v>
+      </c>
+      <c r="X291" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>257</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y291"/>
+  <dimension ref="A1:Y292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23453,6 +23453,85 @@
         <v>257</v>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>200</v>
+      </c>
+      <c r="C292" t="n">
+        <v>103</v>
+      </c>
+      <c r="D292" t="n">
+        <v>100</v>
+      </c>
+      <c r="E292" t="n">
+        <v>102</v>
+      </c>
+      <c r="F292" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" t="n">
+        <v>102</v>
+      </c>
+      <c r="H292" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" t="n">
+        <v>102</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" t="n">
+        <v>101</v>
+      </c>
+      <c r="L292" t="n">
+        <v>0</v>
+      </c>
+      <c r="M292" t="n">
+        <v>101</v>
+      </c>
+      <c r="N292" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="P292" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>1</v>
+      </c>
+      <c r="R292" t="n">
+        <v>0</v>
+      </c>
+      <c r="S292" t="n">
+        <v>1</v>
+      </c>
+      <c r="T292" t="n">
+        <v>0</v>
+      </c>
+      <c r="U292" t="n">
+        <v>1</v>
+      </c>
+      <c r="V292" t="n">
+        <v>0</v>
+      </c>
+      <c r="W292" t="n">
+        <v>1</v>
+      </c>
+      <c r="X292" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y292"/>
+  <dimension ref="A1:Y293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23532,6 +23532,85 @@
         <v>1</v>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>100</v>
+      </c>
+      <c r="C293" t="n">
+        <v>105</v>
+      </c>
+      <c r="D293" t="n">
+        <v>100</v>
+      </c>
+      <c r="E293" t="n">
+        <v>105</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="n">
+        <v>134</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" t="n">
+        <v>135</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="n">
+        <v>135</v>
+      </c>
+      <c r="L293" t="n">
+        <v>0</v>
+      </c>
+      <c r="M293" t="n">
+        <v>135</v>
+      </c>
+      <c r="N293" t="n">
+        <v>0</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
+      <c r="P293" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>1</v>
+      </c>
+      <c r="R293" t="n">
+        <v>0</v>
+      </c>
+      <c r="S293" t="n">
+        <v>1</v>
+      </c>
+      <c r="T293" t="n">
+        <v>0</v>
+      </c>
+      <c r="U293" t="n">
+        <v>1</v>
+      </c>
+      <c r="V293" t="n">
+        <v>0</v>
+      </c>
+      <c r="W293" t="n">
+        <v>1</v>
+      </c>
+      <c r="X293" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y293"/>
+  <dimension ref="A1:Y294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23611,6 +23611,85 @@
         <v>1</v>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>100</v>
+      </c>
+      <c r="C294" t="n">
+        <v>102</v>
+      </c>
+      <c r="D294" t="n">
+        <v>100</v>
+      </c>
+      <c r="E294" t="n">
+        <v>100</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="n">
+        <v>164</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" t="n">
+        <v>164</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="n">
+        <v>164</v>
+      </c>
+      <c r="L294" t="n">
+        <v>0</v>
+      </c>
+      <c r="M294" t="n">
+        <v>166</v>
+      </c>
+      <c r="N294" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
+        <v>8</v>
+      </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>49</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="n">
+        <v>278</v>
+      </c>
+      <c r="T294" t="n">
+        <v>0</v>
+      </c>
+      <c r="U294" t="n">
+        <v>287</v>
+      </c>
+      <c r="V294" t="n">
+        <v>0</v>
+      </c>
+      <c r="W294" t="n">
+        <v>278</v>
+      </c>
+      <c r="X294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>278</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y294"/>
+  <dimension ref="A1:Y295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23690,6 +23690,85 @@
         <v>278</v>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>100</v>
+      </c>
+      <c r="C295" t="n">
+        <v>108</v>
+      </c>
+      <c r="D295" t="n">
+        <v>100</v>
+      </c>
+      <c r="E295" t="n">
+        <v>108</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="n">
+        <v>212</v>
+      </c>
+      <c r="H295" t="n">
+        <v>0</v>
+      </c>
+      <c r="I295" t="n">
+        <v>212</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>212</v>
+      </c>
+      <c r="L295" t="n">
+        <v>0</v>
+      </c>
+      <c r="M295" t="n">
+        <v>212</v>
+      </c>
+      <c r="N295" t="n">
+        <v>0</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0</v>
+      </c>
+      <c r="P295" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>42</v>
+      </c>
+      <c r="R295" t="n">
+        <v>0</v>
+      </c>
+      <c r="S295" t="n">
+        <v>282</v>
+      </c>
+      <c r="T295" t="n">
+        <v>0</v>
+      </c>
+      <c r="U295" t="n">
+        <v>282</v>
+      </c>
+      <c r="V295" t="n">
+        <v>0</v>
+      </c>
+      <c r="W295" t="n">
+        <v>296</v>
+      </c>
+      <c r="X295" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y295"/>
+  <dimension ref="A1:Y296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23769,6 +23769,85 @@
         <v>296</v>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>100</v>
+      </c>
+      <c r="C296" t="n">
+        <v>116</v>
+      </c>
+      <c r="D296" t="n">
+        <v>100</v>
+      </c>
+      <c r="E296" t="n">
+        <v>118</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="n">
+        <v>215</v>
+      </c>
+      <c r="H296" t="n">
+        <v>0</v>
+      </c>
+      <c r="I296" t="n">
+        <v>228</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>228</v>
+      </c>
+      <c r="L296" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" t="n">
+        <v>228</v>
+      </c>
+      <c r="N296" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>35</v>
+      </c>
+      <c r="R296" t="n">
+        <v>0</v>
+      </c>
+      <c r="S296" t="n">
+        <v>278</v>
+      </c>
+      <c r="T296" t="n">
+        <v>0</v>
+      </c>
+      <c r="U296" t="n">
+        <v>296</v>
+      </c>
+      <c r="V296" t="n">
+        <v>0</v>
+      </c>
+      <c r="W296" t="n">
+        <v>278</v>
+      </c>
+      <c r="X296" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>278</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y296"/>
+  <dimension ref="A1:Y297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23848,6 +23848,85 @@
         <v>278</v>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>100</v>
+      </c>
+      <c r="C297" t="n">
+        <v>93</v>
+      </c>
+      <c r="D297" t="n">
+        <v>100</v>
+      </c>
+      <c r="E297" t="n">
+        <v>91</v>
+      </c>
+      <c r="F297" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" t="n">
+        <v>145</v>
+      </c>
+      <c r="H297" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" t="n">
+        <v>151</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" t="n">
+        <v>145</v>
+      </c>
+      <c r="L297" t="n">
+        <v>0</v>
+      </c>
+      <c r="M297" t="n">
+        <v>145</v>
+      </c>
+      <c r="N297" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" t="n">
+        <v>0</v>
+      </c>
+      <c r="P297" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>42</v>
+      </c>
+      <c r="R297" t="n">
+        <v>0</v>
+      </c>
+      <c r="S297" t="n">
+        <v>287</v>
+      </c>
+      <c r="T297" t="n">
+        <v>0</v>
+      </c>
+      <c r="U297" t="n">
+        <v>287</v>
+      </c>
+      <c r="V297" t="n">
+        <v>0</v>
+      </c>
+      <c r="W297" t="n">
+        <v>269</v>
+      </c>
+      <c r="X297" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>269</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y297"/>
+  <dimension ref="A1:Y298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23927,6 +23927,85 @@
         <v>269</v>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>100</v>
+      </c>
+      <c r="C298" t="n">
+        <v>109</v>
+      </c>
+      <c r="D298" t="n">
+        <v>100</v>
+      </c>
+      <c r="E298" t="n">
+        <v>109</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0</v>
+      </c>
+      <c r="G298" t="n">
+        <v>104</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" t="n">
+        <v>98</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
+        <v>104</v>
+      </c>
+      <c r="L298" t="n">
+        <v>0</v>
+      </c>
+      <c r="M298" t="n">
+        <v>104</v>
+      </c>
+      <c r="N298" t="n">
+        <v>0</v>
+      </c>
+      <c r="O298" t="n">
+        <v>0</v>
+      </c>
+      <c r="P298" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>1</v>
+      </c>
+      <c r="R298" t="n">
+        <v>0</v>
+      </c>
+      <c r="S298" t="n">
+        <v>1</v>
+      </c>
+      <c r="T298" t="n">
+        <v>0</v>
+      </c>
+      <c r="U298" t="n">
+        <v>1</v>
+      </c>
+      <c r="V298" t="n">
+        <v>0</v>
+      </c>
+      <c r="W298" t="n">
+        <v>1</v>
+      </c>
+      <c r="X298" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y298"/>
+  <dimension ref="A1:Y299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24006,6 +24006,85 @@
         <v>1</v>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>100</v>
+      </c>
+      <c r="C299" t="n">
+        <v>131</v>
+      </c>
+      <c r="D299" t="n">
+        <v>50</v>
+      </c>
+      <c r="E299" t="n">
+        <v>140</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>114</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0</v>
+      </c>
+      <c r="I299" t="n">
+        <v>114</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
+        <v>114</v>
+      </c>
+      <c r="L299" t="n">
+        <v>0</v>
+      </c>
+      <c r="M299" t="n">
+        <v>110</v>
+      </c>
+      <c r="N299" t="n">
+        <v>0</v>
+      </c>
+      <c r="O299" t="n">
+        <v>0</v>
+      </c>
+      <c r="P299" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>57</v>
+      </c>
+      <c r="R299" t="n">
+        <v>0</v>
+      </c>
+      <c r="S299" t="n">
+        <v>264</v>
+      </c>
+      <c r="T299" t="n">
+        <v>0</v>
+      </c>
+      <c r="U299" t="n">
+        <v>264</v>
+      </c>
+      <c r="V299" t="n">
+        <v>0</v>
+      </c>
+      <c r="W299" t="n">
+        <v>264</v>
+      </c>
+      <c r="X299" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y299"/>
+  <dimension ref="A1:Y300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24085,6 +24085,85 @@
         <v>264</v>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>100</v>
+      </c>
+      <c r="C300" t="n">
+        <v>129</v>
+      </c>
+      <c r="D300" t="n">
+        <v>50</v>
+      </c>
+      <c r="E300" t="n">
+        <v>129</v>
+      </c>
+      <c r="F300" t="n">
+        <v>0</v>
+      </c>
+      <c r="G300" t="n">
+        <v>115</v>
+      </c>
+      <c r="H300" t="n">
+        <v>0</v>
+      </c>
+      <c r="I300" t="n">
+        <v>111</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="n">
+        <v>111</v>
+      </c>
+      <c r="L300" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" t="n">
+        <v>111</v>
+      </c>
+      <c r="N300" t="n">
+        <v>0</v>
+      </c>
+      <c r="O300" t="n">
+        <v>1</v>
+      </c>
+      <c r="P300" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>49</v>
+      </c>
+      <c r="R300" t="n">
+        <v>0</v>
+      </c>
+      <c r="S300" t="n">
+        <v>280</v>
+      </c>
+      <c r="T300" t="n">
+        <v>0</v>
+      </c>
+      <c r="U300" t="n">
+        <v>280</v>
+      </c>
+      <c r="V300" t="n">
+        <v>0</v>
+      </c>
+      <c r="W300" t="n">
+        <v>280</v>
+      </c>
+      <c r="X300" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>280</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y300"/>
+  <dimension ref="A1:Y301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24164,6 +24164,85 @@
         <v>280</v>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>100</v>
+      </c>
+      <c r="C301" t="n">
+        <v>128</v>
+      </c>
+      <c r="D301" t="n">
+        <v>50</v>
+      </c>
+      <c r="E301" t="n">
+        <v>141</v>
+      </c>
+      <c r="F301" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" t="n">
+        <v>142</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" t="n">
+        <v>142</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>142</v>
+      </c>
+      <c r="L301" t="n">
+        <v>0</v>
+      </c>
+      <c r="M301" t="n">
+        <v>142</v>
+      </c>
+      <c r="N301" t="n">
+        <v>0</v>
+      </c>
+      <c r="O301" t="n">
+        <v>1</v>
+      </c>
+      <c r="P301" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>46</v>
+      </c>
+      <c r="R301" t="n">
+        <v>0</v>
+      </c>
+      <c r="S301" t="n">
+        <v>300</v>
+      </c>
+      <c r="T301" t="n">
+        <v>0</v>
+      </c>
+      <c r="U301" t="n">
+        <v>300</v>
+      </c>
+      <c r="V301" t="n">
+        <v>0</v>
+      </c>
+      <c r="W301" t="n">
+        <v>300</v>
+      </c>
+      <c r="X301" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y301"/>
+  <dimension ref="A1:Y302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24243,6 +24243,85 @@
         <v>300</v>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>0</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0</v>
+      </c>
+      <c r="D302" t="n">
+        <v>50</v>
+      </c>
+      <c r="E302" t="n">
+        <v>133</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="n">
+        <v>175</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" t="n">
+        <v>172</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>175</v>
+      </c>
+      <c r="L302" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" t="n">
+        <v>172</v>
+      </c>
+      <c r="N302" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0</v>
+      </c>
+      <c r="P302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>44</v>
+      </c>
+      <c r="R302" t="n">
+        <v>0</v>
+      </c>
+      <c r="S302" t="n">
+        <v>292</v>
+      </c>
+      <c r="T302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U302" t="n">
+        <v>292</v>
+      </c>
+      <c r="V302" t="n">
+        <v>0</v>
+      </c>
+      <c r="W302" t="n">
+        <v>309</v>
+      </c>
+      <c r="X302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>292</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y302"/>
+  <dimension ref="A1:Y303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24322,6 +24322,85 @@
         <v>292</v>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>100</v>
+      </c>
+      <c r="C303" t="n">
+        <v>121</v>
+      </c>
+      <c r="D303" t="n">
+        <v>50</v>
+      </c>
+      <c r="E303" t="n">
+        <v>121</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" t="n">
+        <v>202</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" t="n">
+        <v>206</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" t="n">
+        <v>202</v>
+      </c>
+      <c r="L303" t="n">
+        <v>0</v>
+      </c>
+      <c r="M303" t="n">
+        <v>202</v>
+      </c>
+      <c r="N303" t="n">
+        <v>0</v>
+      </c>
+      <c r="O303" t="n">
+        <v>0</v>
+      </c>
+      <c r="P303" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>39</v>
+      </c>
+      <c r="R303" t="n">
+        <v>0</v>
+      </c>
+      <c r="S303" t="n">
+        <v>297</v>
+      </c>
+      <c r="T303" t="n">
+        <v>0</v>
+      </c>
+      <c r="U303" t="n">
+        <v>297</v>
+      </c>
+      <c r="V303" t="n">
+        <v>0</v>
+      </c>
+      <c r="W303" t="n">
+        <v>297</v>
+      </c>
+      <c r="X303" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>310</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y303"/>
+  <dimension ref="A1:Y304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24401,6 +24401,85 @@
         <v>310</v>
       </c>
     </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>100</v>
+      </c>
+      <c r="C304" t="n">
+        <v>127</v>
+      </c>
+      <c r="D304" t="n">
+        <v>50</v>
+      </c>
+      <c r="E304" t="n">
+        <v>127</v>
+      </c>
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="n">
+        <v>215</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0</v>
+      </c>
+      <c r="I304" t="n">
+        <v>215</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" t="n">
+        <v>215</v>
+      </c>
+      <c r="L304" t="n">
+        <v>0</v>
+      </c>
+      <c r="M304" t="n">
+        <v>215</v>
+      </c>
+      <c r="N304" t="n">
+        <v>0</v>
+      </c>
+      <c r="O304" t="n">
+        <v>0</v>
+      </c>
+      <c r="P304" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>37</v>
+      </c>
+      <c r="R304" t="n">
+        <v>0</v>
+      </c>
+      <c r="S304" t="n">
+        <v>289</v>
+      </c>
+      <c r="T304" t="n">
+        <v>0</v>
+      </c>
+      <c r="U304" t="n">
+        <v>289</v>
+      </c>
+      <c r="V304" t="n">
+        <v>0</v>
+      </c>
+      <c r="W304" t="n">
+        <v>289</v>
+      </c>
+      <c r="X304" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>289</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y304"/>
+  <dimension ref="A1:Y305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24480,6 +24480,85 @@
         <v>289</v>
       </c>
     </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>100</v>
+      </c>
+      <c r="C305" t="n">
+        <v>116</v>
+      </c>
+      <c r="D305" t="n">
+        <v>50</v>
+      </c>
+      <c r="E305" t="n">
+        <v>116</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="n">
+        <v>141</v>
+      </c>
+      <c r="H305" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" t="n">
+        <v>141</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
+        <v>141</v>
+      </c>
+      <c r="L305" t="n">
+        <v>0</v>
+      </c>
+      <c r="M305" t="n">
+        <v>141</v>
+      </c>
+      <c r="N305" t="n">
+        <v>0</v>
+      </c>
+      <c r="O305" t="n">
+        <v>0</v>
+      </c>
+      <c r="P305" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>36</v>
+      </c>
+      <c r="R305" t="n">
+        <v>0</v>
+      </c>
+      <c r="S305" t="n">
+        <v>290</v>
+      </c>
+      <c r="T305" t="n">
+        <v>0</v>
+      </c>
+      <c r="U305" t="n">
+        <v>290</v>
+      </c>
+      <c r="V305" t="n">
+        <v>0</v>
+      </c>
+      <c r="W305" t="n">
+        <v>290</v>
+      </c>
+      <c r="X305" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>290</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y305"/>
+  <dimension ref="A1:Y306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24559,6 +24559,85 @@
         <v>290</v>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>0</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" t="n">
+        <v>50</v>
+      </c>
+      <c r="E306" t="n">
+        <v>108</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0</v>
+      </c>
+      <c r="G306" t="n">
+        <v>175</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" t="n">
+        <v>175</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="n">
+        <v>175</v>
+      </c>
+      <c r="L306" t="n">
+        <v>0</v>
+      </c>
+      <c r="M306" t="n">
+        <v>178</v>
+      </c>
+      <c r="N306" t="n">
+        <v>0</v>
+      </c>
+      <c r="O306" t="n">
+        <v>0</v>
+      </c>
+      <c r="P306" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>39</v>
+      </c>
+      <c r="R306" t="n">
+        <v>0</v>
+      </c>
+      <c r="S306" t="n">
+        <v>291</v>
+      </c>
+      <c r="T306" t="n">
+        <v>0</v>
+      </c>
+      <c r="U306" t="n">
+        <v>291</v>
+      </c>
+      <c r="V306" t="n">
+        <v>0</v>
+      </c>
+      <c r="W306" t="n">
+        <v>291</v>
+      </c>
+      <c r="X306" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>291</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y306"/>
+  <dimension ref="A1:Y307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24638,6 +24638,85 @@
         <v>291</v>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0</v>
+      </c>
+      <c r="D307" t="n">
+        <v>50</v>
+      </c>
+      <c r="E307" t="n">
+        <v>114</v>
+      </c>
+      <c r="F307" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" t="n">
+        <v>199</v>
+      </c>
+      <c r="H307" t="n">
+        <v>0</v>
+      </c>
+      <c r="I307" t="n">
+        <v>206</v>
+      </c>
+      <c r="J307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" t="n">
+        <v>206</v>
+      </c>
+      <c r="L307" t="n">
+        <v>0</v>
+      </c>
+      <c r="M307" t="n">
+        <v>199</v>
+      </c>
+      <c r="N307" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" t="n">
+        <v>0</v>
+      </c>
+      <c r="P307" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>33</v>
+      </c>
+      <c r="R307" t="n">
+        <v>0</v>
+      </c>
+      <c r="S307" t="n">
+        <v>282</v>
+      </c>
+      <c r="T307" t="n">
+        <v>0</v>
+      </c>
+      <c r="U307" t="n">
+        <v>282</v>
+      </c>
+      <c r="V307" t="n">
+        <v>0</v>
+      </c>
+      <c r="W307" t="n">
+        <v>282</v>
+      </c>
+      <c r="X307" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>282</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y307"/>
+  <dimension ref="A1:Y308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24717,6 +24717,85 @@
         <v>282</v>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>100</v>
+      </c>
+      <c r="C308" t="n">
+        <v>130</v>
+      </c>
+      <c r="D308" t="n">
+        <v>50</v>
+      </c>
+      <c r="E308" t="n">
+        <v>130</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="n">
+        <v>154</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" t="n">
+        <v>154</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" t="n">
+        <v>154</v>
+      </c>
+      <c r="L308" t="n">
+        <v>0</v>
+      </c>
+      <c r="M308" t="n">
+        <v>154</v>
+      </c>
+      <c r="N308" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" t="n">
+        <v>0</v>
+      </c>
+      <c r="P308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>42</v>
+      </c>
+      <c r="R308" t="n">
+        <v>0</v>
+      </c>
+      <c r="S308" t="n">
+        <v>297</v>
+      </c>
+      <c r="T308" t="n">
+        <v>0</v>
+      </c>
+      <c r="U308" t="n">
+        <v>297</v>
+      </c>
+      <c r="V308" t="n">
+        <v>0</v>
+      </c>
+      <c r="W308" t="n">
+        <v>297</v>
+      </c>
+      <c r="X308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>297</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y308"/>
+  <dimension ref="A1:Y309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24796,6 +24796,85 @@
         <v>297</v>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" t="n">
+        <v>50</v>
+      </c>
+      <c r="E309" t="n">
+        <v>130</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0</v>
+      </c>
+      <c r="G309" t="n">
+        <v>186</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" t="n">
+        <v>186</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" t="n">
+        <v>186</v>
+      </c>
+      <c r="L309" t="n">
+        <v>0</v>
+      </c>
+      <c r="M309" t="n">
+        <v>186</v>
+      </c>
+      <c r="N309" t="n">
+        <v>0</v>
+      </c>
+      <c r="O309" t="n">
+        <v>0</v>
+      </c>
+      <c r="P309" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>52</v>
+      </c>
+      <c r="R309" t="n">
+        <v>0</v>
+      </c>
+      <c r="S309" t="n">
+        <v>310</v>
+      </c>
+      <c r="T309" t="n">
+        <v>0</v>
+      </c>
+      <c r="U309" t="n">
+        <v>310</v>
+      </c>
+      <c r="V309" t="n">
+        <v>0</v>
+      </c>
+      <c r="W309" t="n">
+        <v>310</v>
+      </c>
+      <c r="X309" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>310</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y309"/>
+  <dimension ref="A1:Y310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24875,6 +24875,85 @@
         <v>310</v>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>0</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" t="n">
+        <v>50</v>
+      </c>
+      <c r="E310" t="n">
+        <v>98</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" t="n">
+        <v>115</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0</v>
+      </c>
+      <c r="I310" t="n">
+        <v>115</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" t="n">
+        <v>115</v>
+      </c>
+      <c r="L310" t="n">
+        <v>0</v>
+      </c>
+      <c r="M310" t="n">
+        <v>115</v>
+      </c>
+      <c r="N310" t="n">
+        <v>0</v>
+      </c>
+      <c r="O310" t="n">
+        <v>0</v>
+      </c>
+      <c r="P310" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>49</v>
+      </c>
+      <c r="R310" t="n">
+        <v>0</v>
+      </c>
+      <c r="S310" t="n">
+        <v>308</v>
+      </c>
+      <c r="T310" t="n">
+        <v>0</v>
+      </c>
+      <c r="U310" t="n">
+        <v>308</v>
+      </c>
+      <c r="V310" t="n">
+        <v>0</v>
+      </c>
+      <c r="W310" t="n">
+        <v>308</v>
+      </c>
+      <c r="X310" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>308</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y310"/>
+  <dimension ref="A1:Y311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24954,6 +24954,85 @@
         <v>308</v>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>0</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0</v>
+      </c>
+      <c r="D311" t="n">
+        <v>50</v>
+      </c>
+      <c r="E311" t="n">
+        <v>83</v>
+      </c>
+      <c r="F311" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" t="n">
+        <v>114</v>
+      </c>
+      <c r="H311" t="n">
+        <v>0</v>
+      </c>
+      <c r="I311" t="n">
+        <v>114</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="n">
+        <v>114</v>
+      </c>
+      <c r="L311" t="n">
+        <v>0</v>
+      </c>
+      <c r="M311" t="n">
+        <v>114</v>
+      </c>
+      <c r="N311" t="n">
+        <v>0</v>
+      </c>
+      <c r="O311" t="n">
+        <v>0</v>
+      </c>
+      <c r="P311" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>48</v>
+      </c>
+      <c r="R311" t="n">
+        <v>0</v>
+      </c>
+      <c r="S311" t="n">
+        <v>302</v>
+      </c>
+      <c r="T311" t="n">
+        <v>0</v>
+      </c>
+      <c r="U311" t="n">
+        <v>302</v>
+      </c>
+      <c r="V311" t="n">
+        <v>0</v>
+      </c>
+      <c r="W311" t="n">
+        <v>302</v>
+      </c>
+      <c r="X311" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>302</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y311"/>
+  <dimension ref="A1:Y312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25033,6 +25033,85 @@
         <v>302</v>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>100</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0</v>
+      </c>
+      <c r="D312" t="n">
+        <v>50</v>
+      </c>
+      <c r="E312" t="n">
+        <v>84</v>
+      </c>
+      <c r="F312" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" t="n">
+        <v>146</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0</v>
+      </c>
+      <c r="I312" t="n">
+        <v>146</v>
+      </c>
+      <c r="J312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" t="n">
+        <v>146</v>
+      </c>
+      <c r="L312" t="n">
+        <v>0</v>
+      </c>
+      <c r="M312" t="n">
+        <v>146</v>
+      </c>
+      <c r="N312" t="n">
+        <v>0</v>
+      </c>
+      <c r="O312" t="n">
+        <v>0</v>
+      </c>
+      <c r="P312" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>39</v>
+      </c>
+      <c r="R312" t="n">
+        <v>0</v>
+      </c>
+      <c r="S312" t="n">
+        <v>298</v>
+      </c>
+      <c r="T312" t="n">
+        <v>0</v>
+      </c>
+      <c r="U312" t="n">
+        <v>298</v>
+      </c>
+      <c r="V312" t="n">
+        <v>0</v>
+      </c>
+      <c r="W312" t="n">
+        <v>298</v>
+      </c>
+      <c r="X312" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>298</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y312"/>
+  <dimension ref="A1:Y313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25112,6 +25112,85 @@
         <v>298</v>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>0</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0</v>
+      </c>
+      <c r="D313" t="n">
+        <v>50</v>
+      </c>
+      <c r="E313" t="n">
+        <v>77</v>
+      </c>
+      <c r="F313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" t="n">
+        <v>134</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0</v>
+      </c>
+      <c r="I313" t="n">
+        <v>134</v>
+      </c>
+      <c r="J313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" t="n">
+        <v>134</v>
+      </c>
+      <c r="L313" t="n">
+        <v>0</v>
+      </c>
+      <c r="M313" t="n">
+        <v>134</v>
+      </c>
+      <c r="N313" t="n">
+        <v>0</v>
+      </c>
+      <c r="O313" t="n">
+        <v>0</v>
+      </c>
+      <c r="P313" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>40</v>
+      </c>
+      <c r="R313" t="n">
+        <v>0</v>
+      </c>
+      <c r="S313" t="n">
+        <v>293</v>
+      </c>
+      <c r="T313" t="n">
+        <v>0</v>
+      </c>
+      <c r="U313" t="n">
+        <v>293</v>
+      </c>
+      <c r="V313" t="n">
+        <v>0</v>
+      </c>
+      <c r="W313" t="n">
+        <v>293</v>
+      </c>
+      <c r="X313" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>293</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y313"/>
+  <dimension ref="A1:Y314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25191,6 +25191,85 @@
         <v>293</v>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>100</v>
+      </c>
+      <c r="C314" t="n">
+        <v>79</v>
+      </c>
+      <c r="D314" t="n">
+        <v>50</v>
+      </c>
+      <c r="E314" t="n">
+        <v>79</v>
+      </c>
+      <c r="F314" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" t="n">
+        <v>172</v>
+      </c>
+      <c r="H314" t="n">
+        <v>0</v>
+      </c>
+      <c r="I314" t="n">
+        <v>172</v>
+      </c>
+      <c r="J314" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" t="n">
+        <v>172</v>
+      </c>
+      <c r="L314" t="n">
+        <v>0</v>
+      </c>
+      <c r="M314" t="n">
+        <v>172</v>
+      </c>
+      <c r="N314" t="n">
+        <v>0</v>
+      </c>
+      <c r="O314" t="n">
+        <v>0</v>
+      </c>
+      <c r="P314" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>25</v>
+      </c>
+      <c r="R314" t="n">
+        <v>0</v>
+      </c>
+      <c r="S314" t="n">
+        <v>168</v>
+      </c>
+      <c r="T314" t="n">
+        <v>0</v>
+      </c>
+      <c r="U314" t="n">
+        <v>168</v>
+      </c>
+      <c r="V314" t="n">
+        <v>0</v>
+      </c>
+      <c r="W314" t="n">
+        <v>168</v>
+      </c>
+      <c r="X314" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y314"/>
+  <dimension ref="A1:Y315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25270,6 +25270,85 @@
         <v>168</v>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>100</v>
+      </c>
+      <c r="C315" t="n">
+        <v>88</v>
+      </c>
+      <c r="D315" t="n">
+        <v>50</v>
+      </c>
+      <c r="E315" t="n">
+        <v>88</v>
+      </c>
+      <c r="F315" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" t="n">
+        <v>133</v>
+      </c>
+      <c r="H315" t="n">
+        <v>0</v>
+      </c>
+      <c r="I315" t="n">
+        <v>133</v>
+      </c>
+      <c r="J315" t="n">
+        <v>0</v>
+      </c>
+      <c r="K315" t="n">
+        <v>133</v>
+      </c>
+      <c r="L315" t="n">
+        <v>0</v>
+      </c>
+      <c r="M315" t="n">
+        <v>133</v>
+      </c>
+      <c r="N315" t="n">
+        <v>0</v>
+      </c>
+      <c r="O315" t="n">
+        <v>0</v>
+      </c>
+      <c r="P315" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>27</v>
+      </c>
+      <c r="R315" t="n">
+        <v>0</v>
+      </c>
+      <c r="S315" t="n">
+        <v>204</v>
+      </c>
+      <c r="T315" t="n">
+        <v>0</v>
+      </c>
+      <c r="U315" t="n">
+        <v>204</v>
+      </c>
+      <c r="V315" t="n">
+        <v>0</v>
+      </c>
+      <c r="W315" t="n">
+        <v>204</v>
+      </c>
+      <c r="X315" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>204</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y315"/>
+  <dimension ref="A1:Y316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25349,6 +25349,85 @@
         <v>204</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>100</v>
+      </c>
+      <c r="C316" t="n">
+        <v>91</v>
+      </c>
+      <c r="D316" t="n">
+        <v>50</v>
+      </c>
+      <c r="E316" t="n">
+        <v>91</v>
+      </c>
+      <c r="F316" t="n">
+        <v>0</v>
+      </c>
+      <c r="G316" t="n">
+        <v>139</v>
+      </c>
+      <c r="H316" t="n">
+        <v>0</v>
+      </c>
+      <c r="I316" t="n">
+        <v>139</v>
+      </c>
+      <c r="J316" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" t="n">
+        <v>139</v>
+      </c>
+      <c r="L316" t="n">
+        <v>0</v>
+      </c>
+      <c r="M316" t="n">
+        <v>139</v>
+      </c>
+      <c r="N316" t="n">
+        <v>0</v>
+      </c>
+      <c r="O316" t="n">
+        <v>0</v>
+      </c>
+      <c r="P316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>28</v>
+      </c>
+      <c r="R316" t="n">
+        <v>0</v>
+      </c>
+      <c r="S316" t="n">
+        <v>255</v>
+      </c>
+      <c r="T316" t="n">
+        <v>0</v>
+      </c>
+      <c r="U316" t="n">
+        <v>255</v>
+      </c>
+      <c r="V316" t="n">
+        <v>0</v>
+      </c>
+      <c r="W316" t="n">
+        <v>255</v>
+      </c>
+      <c r="X316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>255</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y316"/>
+  <dimension ref="A1:Y317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25428,6 +25428,85 @@
         <v>255</v>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>100</v>
+      </c>
+      <c r="C317" t="n">
+        <v>88</v>
+      </c>
+      <c r="D317" t="n">
+        <v>50</v>
+      </c>
+      <c r="E317" t="n">
+        <v>88</v>
+      </c>
+      <c r="F317" t="n">
+        <v>0</v>
+      </c>
+      <c r="G317" t="n">
+        <v>105</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0</v>
+      </c>
+      <c r="I317" t="n">
+        <v>105</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" t="n">
+        <v>105</v>
+      </c>
+      <c r="L317" t="n">
+        <v>0</v>
+      </c>
+      <c r="M317" t="n">
+        <v>105</v>
+      </c>
+      <c r="N317" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" t="n">
+        <v>0</v>
+      </c>
+      <c r="P317" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>30</v>
+      </c>
+      <c r="R317" t="n">
+        <v>0</v>
+      </c>
+      <c r="S317" t="n">
+        <v>289</v>
+      </c>
+      <c r="T317" t="n">
+        <v>0</v>
+      </c>
+      <c r="U317" t="n">
+        <v>289</v>
+      </c>
+      <c r="V317" t="n">
+        <v>0</v>
+      </c>
+      <c r="W317" t="n">
+        <v>289</v>
+      </c>
+      <c r="X317" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>289</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y317"/>
+  <dimension ref="A1:Y318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25507,6 +25507,85 @@
         <v>289</v>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>100</v>
+      </c>
+      <c r="C318" t="n">
+        <v>92</v>
+      </c>
+      <c r="D318" t="n">
+        <v>50</v>
+      </c>
+      <c r="E318" t="n">
+        <v>92</v>
+      </c>
+      <c r="F318" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" t="n">
+        <v>129</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0</v>
+      </c>
+      <c r="I318" t="n">
+        <v>129</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" t="n">
+        <v>129</v>
+      </c>
+      <c r="L318" t="n">
+        <v>0</v>
+      </c>
+      <c r="M318" t="n">
+        <v>129</v>
+      </c>
+      <c r="N318" t="n">
+        <v>0</v>
+      </c>
+      <c r="O318" t="n">
+        <v>0</v>
+      </c>
+      <c r="P318" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>33</v>
+      </c>
+      <c r="R318" t="n">
+        <v>0</v>
+      </c>
+      <c r="S318" t="n">
+        <v>298</v>
+      </c>
+      <c r="T318" t="n">
+        <v>0</v>
+      </c>
+      <c r="U318" t="n">
+        <v>298</v>
+      </c>
+      <c r="V318" t="n">
+        <v>0</v>
+      </c>
+      <c r="W318" t="n">
+        <v>298</v>
+      </c>
+      <c r="X318" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>298</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y318"/>
+  <dimension ref="A1:Y319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25586,6 +25586,85 @@
         <v>298</v>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>100</v>
+      </c>
+      <c r="C319" t="n">
+        <v>98</v>
+      </c>
+      <c r="D319" t="n">
+        <v>50</v>
+      </c>
+      <c r="E319" t="n">
+        <v>98</v>
+      </c>
+      <c r="F319" t="n">
+        <v>0</v>
+      </c>
+      <c r="G319" t="n">
+        <v>127</v>
+      </c>
+      <c r="H319" t="n">
+        <v>0</v>
+      </c>
+      <c r="I319" t="n">
+        <v>127</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" t="n">
+        <v>127</v>
+      </c>
+      <c r="L319" t="n">
+        <v>0</v>
+      </c>
+      <c r="M319" t="n">
+        <v>127</v>
+      </c>
+      <c r="N319" t="n">
+        <v>0</v>
+      </c>
+      <c r="O319" t="n">
+        <v>3</v>
+      </c>
+      <c r="P319" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>34</v>
+      </c>
+      <c r="R319" t="n">
+        <v>0</v>
+      </c>
+      <c r="S319" t="n">
+        <v>301</v>
+      </c>
+      <c r="T319" t="n">
+        <v>0</v>
+      </c>
+      <c r="U319" t="n">
+        <v>301</v>
+      </c>
+      <c r="V319" t="n">
+        <v>0</v>
+      </c>
+      <c r="W319" t="n">
+        <v>301</v>
+      </c>
+      <c r="X319" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>301</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y319"/>
+  <dimension ref="A1:Y320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25665,6 +25665,85 @@
         <v>301</v>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>100</v>
+      </c>
+      <c r="C320" t="n">
+        <v>103</v>
+      </c>
+      <c r="D320" t="n">
+        <v>50</v>
+      </c>
+      <c r="E320" t="n">
+        <v>103</v>
+      </c>
+      <c r="F320" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" t="n">
+        <v>88</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0</v>
+      </c>
+      <c r="I320" t="n">
+        <v>88</v>
+      </c>
+      <c r="J320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" t="n">
+        <v>88</v>
+      </c>
+      <c r="L320" t="n">
+        <v>0</v>
+      </c>
+      <c r="M320" t="n">
+        <v>88</v>
+      </c>
+      <c r="N320" t="n">
+        <v>0</v>
+      </c>
+      <c r="O320" t="n">
+        <v>0</v>
+      </c>
+      <c r="P320" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>32</v>
+      </c>
+      <c r="R320" t="n">
+        <v>0</v>
+      </c>
+      <c r="S320" t="n">
+        <v>303</v>
+      </c>
+      <c r="T320" t="n">
+        <v>0</v>
+      </c>
+      <c r="U320" t="n">
+        <v>303</v>
+      </c>
+      <c r="V320" t="n">
+        <v>0</v>
+      </c>
+      <c r="W320" t="n">
+        <v>303</v>
+      </c>
+      <c r="X320" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>303</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y320"/>
+  <dimension ref="A1:Y321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25744,6 +25744,85 @@
         <v>303</v>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>100</v>
+      </c>
+      <c r="C321" t="n">
+        <v>114</v>
+      </c>
+      <c r="D321" t="n">
+        <v>50</v>
+      </c>
+      <c r="E321" t="n">
+        <v>114</v>
+      </c>
+      <c r="F321" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" t="n">
+        <v>78</v>
+      </c>
+      <c r="H321" t="n">
+        <v>0</v>
+      </c>
+      <c r="I321" t="n">
+        <v>78</v>
+      </c>
+      <c r="J321" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" t="n">
+        <v>74</v>
+      </c>
+      <c r="L321" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" t="n">
+        <v>78</v>
+      </c>
+      <c r="N321" t="n">
+        <v>0</v>
+      </c>
+      <c r="O321" t="n">
+        <v>0</v>
+      </c>
+      <c r="P321" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>35</v>
+      </c>
+      <c r="R321" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" t="n">
+        <v>299</v>
+      </c>
+      <c r="T321" t="n">
+        <v>0</v>
+      </c>
+      <c r="U321" t="n">
+        <v>299</v>
+      </c>
+      <c r="V321" t="n">
+        <v>0</v>
+      </c>
+      <c r="W321" t="n">
+        <v>299</v>
+      </c>
+      <c r="X321" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y321"/>
+  <dimension ref="A1:Y322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25823,6 +25823,85 @@
         <v>299</v>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>100</v>
+      </c>
+      <c r="C322" t="n">
+        <v>109</v>
+      </c>
+      <c r="D322" t="n">
+        <v>50</v>
+      </c>
+      <c r="E322" t="n">
+        <v>108</v>
+      </c>
+      <c r="F322" t="n">
+        <v>0</v>
+      </c>
+      <c r="G322" t="n">
+        <v>92</v>
+      </c>
+      <c r="H322" t="n">
+        <v>0</v>
+      </c>
+      <c r="I322" t="n">
+        <v>92</v>
+      </c>
+      <c r="J322" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" t="n">
+        <v>85</v>
+      </c>
+      <c r="L322" t="n">
+        <v>0</v>
+      </c>
+      <c r="M322" t="n">
+        <v>92</v>
+      </c>
+      <c r="N322" t="n">
+        <v>0</v>
+      </c>
+      <c r="O322" t="n">
+        <v>0</v>
+      </c>
+      <c r="P322" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>33</v>
+      </c>
+      <c r="R322" t="n">
+        <v>0</v>
+      </c>
+      <c r="S322" t="n">
+        <v>106</v>
+      </c>
+      <c r="T322" t="n">
+        <v>0</v>
+      </c>
+      <c r="U322" t="n">
+        <v>106</v>
+      </c>
+      <c r="V322" t="n">
+        <v>0</v>
+      </c>
+      <c r="W322" t="n">
+        <v>106</v>
+      </c>
+      <c r="X322" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y322"/>
+  <dimension ref="A1:Y323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25902,6 +25902,85 @@
         <v>106</v>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>0</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" t="n">
+        <v>50</v>
+      </c>
+      <c r="E323" t="n">
+        <v>109</v>
+      </c>
+      <c r="F323" t="n">
+        <v>0</v>
+      </c>
+      <c r="G323" t="n">
+        <v>105</v>
+      </c>
+      <c r="H323" t="n">
+        <v>0</v>
+      </c>
+      <c r="I323" t="n">
+        <v>98</v>
+      </c>
+      <c r="J323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" t="n">
+        <v>98</v>
+      </c>
+      <c r="L323" t="n">
+        <v>0</v>
+      </c>
+      <c r="M323" t="n">
+        <v>98</v>
+      </c>
+      <c r="N323" t="n">
+        <v>0</v>
+      </c>
+      <c r="O323" t="n">
+        <v>0</v>
+      </c>
+      <c r="P323" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>36</v>
+      </c>
+      <c r="R323" t="n">
+        <v>0</v>
+      </c>
+      <c r="S323" t="n">
+        <v>151</v>
+      </c>
+      <c r="T323" t="n">
+        <v>0</v>
+      </c>
+      <c r="U323" t="n">
+        <v>151</v>
+      </c>
+      <c r="V323" t="n">
+        <v>0</v>
+      </c>
+      <c r="W323" t="n">
+        <v>151</v>
+      </c>
+      <c r="X323" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y323"/>
+  <dimension ref="A1:Y324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25981,6 +25981,85 @@
         <v>151</v>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>100</v>
+      </c>
+      <c r="C324" t="n">
+        <v>121</v>
+      </c>
+      <c r="D324" t="n">
+        <v>50</v>
+      </c>
+      <c r="E324" t="n">
+        <v>123</v>
+      </c>
+      <c r="F324" t="n">
+        <v>0</v>
+      </c>
+      <c r="G324" t="n">
+        <v>136</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0</v>
+      </c>
+      <c r="I324" t="n">
+        <v>136</v>
+      </c>
+      <c r="J324" t="n">
+        <v>0</v>
+      </c>
+      <c r="K324" t="n">
+        <v>135</v>
+      </c>
+      <c r="L324" t="n">
+        <v>0</v>
+      </c>
+      <c r="M324" t="n">
+        <v>135</v>
+      </c>
+      <c r="N324" t="n">
+        <v>0</v>
+      </c>
+      <c r="O324" t="n">
+        <v>0</v>
+      </c>
+      <c r="P324" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>43</v>
+      </c>
+      <c r="R324" t="n">
+        <v>0</v>
+      </c>
+      <c r="S324" t="n">
+        <v>178</v>
+      </c>
+      <c r="T324" t="n">
+        <v>0</v>
+      </c>
+      <c r="U324" t="n">
+        <v>178</v>
+      </c>
+      <c r="V324" t="n">
+        <v>0</v>
+      </c>
+      <c r="W324" t="n">
+        <v>178</v>
+      </c>
+      <c r="X324" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>178</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y324"/>
+  <dimension ref="A1:Y325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26060,6 +26060,85 @@
         <v>178</v>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>100</v>
+      </c>
+      <c r="C325" t="n">
+        <v>95</v>
+      </c>
+      <c r="D325" t="n">
+        <v>50</v>
+      </c>
+      <c r="E325" t="n">
+        <v>95</v>
+      </c>
+      <c r="F325" t="n">
+        <v>0</v>
+      </c>
+      <c r="G325" t="n">
+        <v>160</v>
+      </c>
+      <c r="H325" t="n">
+        <v>0</v>
+      </c>
+      <c r="I325" t="n">
+        <v>176</v>
+      </c>
+      <c r="J325" t="n">
+        <v>0</v>
+      </c>
+      <c r="K325" t="n">
+        <v>176</v>
+      </c>
+      <c r="L325" t="n">
+        <v>0</v>
+      </c>
+      <c r="M325" t="n">
+        <v>160</v>
+      </c>
+      <c r="N325" t="n">
+        <v>0</v>
+      </c>
+      <c r="O325" t="n">
+        <v>0</v>
+      </c>
+      <c r="P325" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>30</v>
+      </c>
+      <c r="R325" t="n">
+        <v>0</v>
+      </c>
+      <c r="S325" t="n">
+        <v>138</v>
+      </c>
+      <c r="T325" t="n">
+        <v>0</v>
+      </c>
+      <c r="U325" t="n">
+        <v>138</v>
+      </c>
+      <c r="V325" t="n">
+        <v>0</v>
+      </c>
+      <c r="W325" t="n">
+        <v>138</v>
+      </c>
+      <c r="X325" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y325"/>
+  <dimension ref="A1:Y326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26139,6 +26139,85 @@
         <v>138</v>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>100</v>
+      </c>
+      <c r="C326" t="n">
+        <v>90</v>
+      </c>
+      <c r="D326" t="n">
+        <v>50</v>
+      </c>
+      <c r="E326" t="n">
+        <v>93</v>
+      </c>
+      <c r="F326" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" t="n">
+        <v>193</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0</v>
+      </c>
+      <c r="I326" t="n">
+        <v>198</v>
+      </c>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" t="n">
+        <v>193</v>
+      </c>
+      <c r="L326" t="n">
+        <v>0</v>
+      </c>
+      <c r="M326" t="n">
+        <v>193</v>
+      </c>
+      <c r="N326" t="n">
+        <v>0</v>
+      </c>
+      <c r="O326" t="n">
+        <v>0</v>
+      </c>
+      <c r="P326" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>34</v>
+      </c>
+      <c r="R326" t="n">
+        <v>0</v>
+      </c>
+      <c r="S326" t="n">
+        <v>179</v>
+      </c>
+      <c r="T326" t="n">
+        <v>0</v>
+      </c>
+      <c r="U326" t="n">
+        <v>179</v>
+      </c>
+      <c r="V326" t="n">
+        <v>0</v>
+      </c>
+      <c r="W326" t="n">
+        <v>179</v>
+      </c>
+      <c r="X326" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>179</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y326"/>
+  <dimension ref="A1:Y327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26218,6 +26218,85 @@
         <v>179</v>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>100</v>
+      </c>
+      <c r="C327" t="n">
+        <v>100</v>
+      </c>
+      <c r="D327" t="n">
+        <v>50</v>
+      </c>
+      <c r="E327" t="n">
+        <v>99</v>
+      </c>
+      <c r="F327" t="n">
+        <v>0</v>
+      </c>
+      <c r="G327" t="n">
+        <v>217</v>
+      </c>
+      <c r="H327" t="n">
+        <v>0</v>
+      </c>
+      <c r="I327" t="n">
+        <v>230</v>
+      </c>
+      <c r="J327" t="n">
+        <v>0</v>
+      </c>
+      <c r="K327" t="n">
+        <v>217</v>
+      </c>
+      <c r="L327" t="n">
+        <v>0</v>
+      </c>
+      <c r="M327" t="n">
+        <v>230</v>
+      </c>
+      <c r="N327" t="n">
+        <v>0</v>
+      </c>
+      <c r="O327" t="n">
+        <v>0</v>
+      </c>
+      <c r="P327" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>38</v>
+      </c>
+      <c r="R327" t="n">
+        <v>0</v>
+      </c>
+      <c r="S327" t="n">
+        <v>212</v>
+      </c>
+      <c r="T327" t="n">
+        <v>0</v>
+      </c>
+      <c r="U327" t="n">
+        <v>212</v>
+      </c>
+      <c r="V327" t="n">
+        <v>0</v>
+      </c>
+      <c r="W327" t="n">
+        <v>212</v>
+      </c>
+      <c r="X327" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>212</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y327"/>
+  <dimension ref="A1:Y328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26297,6 +26297,85 @@
         <v>212</v>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>100</v>
+      </c>
+      <c r="C328" t="n">
+        <v>105</v>
+      </c>
+      <c r="D328" t="n">
+        <v>50</v>
+      </c>
+      <c r="E328" t="n">
+        <v>105</v>
+      </c>
+      <c r="F328" t="n">
+        <v>0</v>
+      </c>
+      <c r="G328" t="n">
+        <v>216</v>
+      </c>
+      <c r="H328" t="n">
+        <v>0</v>
+      </c>
+      <c r="I328" t="n">
+        <v>216</v>
+      </c>
+      <c r="J328" t="n">
+        <v>0</v>
+      </c>
+      <c r="K328" t="n">
+        <v>216</v>
+      </c>
+      <c r="L328" t="n">
+        <v>0</v>
+      </c>
+      <c r="M328" t="n">
+        <v>239</v>
+      </c>
+      <c r="N328" t="n">
+        <v>0</v>
+      </c>
+      <c r="O328" t="n">
+        <v>0</v>
+      </c>
+      <c r="P328" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>37</v>
+      </c>
+      <c r="R328" t="n">
+        <v>0</v>
+      </c>
+      <c r="S328" t="n">
+        <v>243</v>
+      </c>
+      <c r="T328" t="n">
+        <v>0</v>
+      </c>
+      <c r="U328" t="n">
+        <v>243</v>
+      </c>
+      <c r="V328" t="n">
+        <v>0</v>
+      </c>
+      <c r="W328" t="n">
+        <v>243</v>
+      </c>
+      <c r="X328" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>243</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y328"/>
+  <dimension ref="A1:Y329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26376,6 +26376,85 @@
         <v>243</v>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>100</v>
+      </c>
+      <c r="C329" t="n">
+        <v>120</v>
+      </c>
+      <c r="D329" t="n">
+        <v>50</v>
+      </c>
+      <c r="E329" t="n">
+        <v>126</v>
+      </c>
+      <c r="F329" t="n">
+        <v>0</v>
+      </c>
+      <c r="G329" t="n">
+        <v>228</v>
+      </c>
+      <c r="H329" t="n">
+        <v>0</v>
+      </c>
+      <c r="I329" t="n">
+        <v>228</v>
+      </c>
+      <c r="J329" t="n">
+        <v>0</v>
+      </c>
+      <c r="K329" t="n">
+        <v>228</v>
+      </c>
+      <c r="L329" t="n">
+        <v>0</v>
+      </c>
+      <c r="M329" t="n">
+        <v>228</v>
+      </c>
+      <c r="N329" t="n">
+        <v>0</v>
+      </c>
+      <c r="O329" t="n">
+        <v>0</v>
+      </c>
+      <c r="P329" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>40</v>
+      </c>
+      <c r="R329" t="n">
+        <v>0</v>
+      </c>
+      <c r="S329" t="n">
+        <v>245</v>
+      </c>
+      <c r="T329" t="n">
+        <v>0</v>
+      </c>
+      <c r="U329" t="n">
+        <v>245</v>
+      </c>
+      <c r="V329" t="n">
+        <v>0</v>
+      </c>
+      <c r="W329" t="n">
+        <v>245</v>
+      </c>
+      <c r="X329" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>245</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y329"/>
+  <dimension ref="A1:Y330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26455,6 +26455,85 @@
         <v>245</v>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>100</v>
+      </c>
+      <c r="C330" t="n">
+        <v>127</v>
+      </c>
+      <c r="D330" t="n">
+        <v>50</v>
+      </c>
+      <c r="E330" t="n">
+        <v>127</v>
+      </c>
+      <c r="F330" t="n">
+        <v>0</v>
+      </c>
+      <c r="G330" t="n">
+        <v>235</v>
+      </c>
+      <c r="H330" t="n">
+        <v>0</v>
+      </c>
+      <c r="I330" t="n">
+        <v>235</v>
+      </c>
+      <c r="J330" t="n">
+        <v>0</v>
+      </c>
+      <c r="K330" t="n">
+        <v>235</v>
+      </c>
+      <c r="L330" t="n">
+        <v>0</v>
+      </c>
+      <c r="M330" t="n">
+        <v>235</v>
+      </c>
+      <c r="N330" t="n">
+        <v>0</v>
+      </c>
+      <c r="O330" t="n">
+        <v>0</v>
+      </c>
+      <c r="P330" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>41</v>
+      </c>
+      <c r="R330" t="n">
+        <v>0</v>
+      </c>
+      <c r="S330" t="n">
+        <v>250</v>
+      </c>
+      <c r="T330" t="n">
+        <v>0</v>
+      </c>
+      <c r="U330" t="n">
+        <v>250</v>
+      </c>
+      <c r="V330" t="n">
+        <v>0</v>
+      </c>
+      <c r="W330" t="n">
+        <v>250</v>
+      </c>
+      <c r="X330" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y330"/>
+  <dimension ref="A1:Y333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26534,6 +26534,243 @@
         <v>250</v>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>100</v>
+      </c>
+      <c r="C331" t="n">
+        <v>154</v>
+      </c>
+      <c r="D331" t="n">
+        <v>50</v>
+      </c>
+      <c r="E331" t="n">
+        <v>154</v>
+      </c>
+      <c r="F331" t="n">
+        <v>0</v>
+      </c>
+      <c r="G331" t="n">
+        <v>239</v>
+      </c>
+      <c r="H331" t="n">
+        <v>0</v>
+      </c>
+      <c r="I331" t="n">
+        <v>263</v>
+      </c>
+      <c r="J331" t="n">
+        <v>0</v>
+      </c>
+      <c r="K331" t="n">
+        <v>239</v>
+      </c>
+      <c r="L331" t="n">
+        <v>0</v>
+      </c>
+      <c r="M331" t="n">
+        <v>239</v>
+      </c>
+      <c r="N331" t="n">
+        <v>0</v>
+      </c>
+      <c r="O331" t="n">
+        <v>0</v>
+      </c>
+      <c r="P331" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>37</v>
+      </c>
+      <c r="R331" t="n">
+        <v>0</v>
+      </c>
+      <c r="S331" t="n">
+        <v>148</v>
+      </c>
+      <c r="T331" t="n">
+        <v>0</v>
+      </c>
+      <c r="U331" t="n">
+        <v>148</v>
+      </c>
+      <c r="V331" t="n">
+        <v>0</v>
+      </c>
+      <c r="W331" t="n">
+        <v>148</v>
+      </c>
+      <c r="X331" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>100</v>
+      </c>
+      <c r="C332" t="n">
+        <v>132</v>
+      </c>
+      <c r="D332" t="n">
+        <v>50</v>
+      </c>
+      <c r="E332" t="n">
+        <v>141</v>
+      </c>
+      <c r="F332" t="n">
+        <v>0</v>
+      </c>
+      <c r="G332" t="n">
+        <v>247</v>
+      </c>
+      <c r="H332" t="n">
+        <v>0</v>
+      </c>
+      <c r="I332" t="n">
+        <v>247</v>
+      </c>
+      <c r="J332" t="n">
+        <v>0</v>
+      </c>
+      <c r="K332" t="n">
+        <v>247</v>
+      </c>
+      <c r="L332" t="n">
+        <v>0</v>
+      </c>
+      <c r="M332" t="n">
+        <v>265</v>
+      </c>
+      <c r="N332" t="n">
+        <v>0</v>
+      </c>
+      <c r="O332" t="n">
+        <v>0</v>
+      </c>
+      <c r="P332" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>46</v>
+      </c>
+      <c r="R332" t="n">
+        <v>0</v>
+      </c>
+      <c r="S332" t="n">
+        <v>197</v>
+      </c>
+      <c r="T332" t="n">
+        <v>0</v>
+      </c>
+      <c r="U332" t="n">
+        <v>197</v>
+      </c>
+      <c r="V332" t="n">
+        <v>0</v>
+      </c>
+      <c r="W332" t="n">
+        <v>197</v>
+      </c>
+      <c r="X332" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>100</v>
+      </c>
+      <c r="C333" t="n">
+        <v>135</v>
+      </c>
+      <c r="D333" t="n">
+        <v>50</v>
+      </c>
+      <c r="E333" t="n">
+        <v>135</v>
+      </c>
+      <c r="F333" t="n">
+        <v>0</v>
+      </c>
+      <c r="G333" t="n">
+        <v>245</v>
+      </c>
+      <c r="H333" t="n">
+        <v>0</v>
+      </c>
+      <c r="I333" t="n">
+        <v>245</v>
+      </c>
+      <c r="J333" t="n">
+        <v>0</v>
+      </c>
+      <c r="K333" t="n">
+        <v>245</v>
+      </c>
+      <c r="L333" t="n">
+        <v>0</v>
+      </c>
+      <c r="M333" t="n">
+        <v>245</v>
+      </c>
+      <c r="N333" t="n">
+        <v>0</v>
+      </c>
+      <c r="O333" t="n">
+        <v>0</v>
+      </c>
+      <c r="P333" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>55</v>
+      </c>
+      <c r="R333" t="n">
+        <v>0</v>
+      </c>
+      <c r="S333" t="n">
+        <v>141</v>
+      </c>
+      <c r="T333" t="n">
+        <v>0</v>
+      </c>
+      <c r="U333" t="n">
+        <v>141</v>
+      </c>
+      <c r="V333" t="n">
+        <v>0</v>
+      </c>
+      <c r="W333" t="n">
+        <v>141</v>
+      </c>
+      <c r="X333" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y333"/>
+  <dimension ref="A1:Y334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26771,6 +26771,85 @@
         <v>141</v>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>100</v>
+      </c>
+      <c r="C334" t="n">
+        <v>138</v>
+      </c>
+      <c r="D334" t="n">
+        <v>50</v>
+      </c>
+      <c r="E334" t="n">
+        <v>133</v>
+      </c>
+      <c r="F334" t="n">
+        <v>0</v>
+      </c>
+      <c r="G334" t="n">
+        <v>247</v>
+      </c>
+      <c r="H334" t="n">
+        <v>0</v>
+      </c>
+      <c r="I334" t="n">
+        <v>247</v>
+      </c>
+      <c r="J334" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" t="n">
+        <v>247</v>
+      </c>
+      <c r="L334" t="n">
+        <v>0</v>
+      </c>
+      <c r="M334" t="n">
+        <v>247</v>
+      </c>
+      <c r="N334" t="n">
+        <v>0</v>
+      </c>
+      <c r="O334" t="n">
+        <v>0</v>
+      </c>
+      <c r="P334" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>37</v>
+      </c>
+      <c r="R334" t="n">
+        <v>0</v>
+      </c>
+      <c r="S334" t="n">
+        <v>78</v>
+      </c>
+      <c r="T334" t="n">
+        <v>0</v>
+      </c>
+      <c r="U334" t="n">
+        <v>78</v>
+      </c>
+      <c r="V334" t="n">
+        <v>0</v>
+      </c>
+      <c r="W334" t="n">
+        <v>78</v>
+      </c>
+      <c r="X334" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y334"/>
+  <dimension ref="A1:Y335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26850,6 +26850,85 @@
         <v>78</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>0</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0</v>
+      </c>
+      <c r="D335" t="n">
+        <v>50</v>
+      </c>
+      <c r="E335" t="n">
+        <v>108</v>
+      </c>
+      <c r="F335" t="n">
+        <v>0</v>
+      </c>
+      <c r="G335" t="n">
+        <v>251</v>
+      </c>
+      <c r="H335" t="n">
+        <v>0</v>
+      </c>
+      <c r="I335" t="n">
+        <v>251</v>
+      </c>
+      <c r="J335" t="n">
+        <v>0</v>
+      </c>
+      <c r="K335" t="n">
+        <v>251</v>
+      </c>
+      <c r="L335" t="n">
+        <v>0</v>
+      </c>
+      <c r="M335" t="n">
+        <v>251</v>
+      </c>
+      <c r="N335" t="n">
+        <v>0</v>
+      </c>
+      <c r="O335" t="n">
+        <v>0</v>
+      </c>
+      <c r="P335" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>35</v>
+      </c>
+      <c r="R335" t="n">
+        <v>0</v>
+      </c>
+      <c r="S335" t="n">
+        <v>121</v>
+      </c>
+      <c r="T335" t="n">
+        <v>0</v>
+      </c>
+      <c r="U335" t="n">
+        <v>121</v>
+      </c>
+      <c r="V335" t="n">
+        <v>0</v>
+      </c>
+      <c r="W335" t="n">
+        <v>121</v>
+      </c>
+      <c r="X335" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y335"/>
+  <dimension ref="A1:Y336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26929,6 +26929,85 @@
         <v>121</v>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>0</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0</v>
+      </c>
+      <c r="D336" t="n">
+        <v>50</v>
+      </c>
+      <c r="E336" t="n">
+        <v>110</v>
+      </c>
+      <c r="F336" t="n">
+        <v>0</v>
+      </c>
+      <c r="G336" t="n">
+        <v>152</v>
+      </c>
+      <c r="H336" t="n">
+        <v>0</v>
+      </c>
+      <c r="I336" t="n">
+        <v>152</v>
+      </c>
+      <c r="J336" t="n">
+        <v>0</v>
+      </c>
+      <c r="K336" t="n">
+        <v>152</v>
+      </c>
+      <c r="L336" t="n">
+        <v>0</v>
+      </c>
+      <c r="M336" t="n">
+        <v>152</v>
+      </c>
+      <c r="N336" t="n">
+        <v>0</v>
+      </c>
+      <c r="O336" t="n">
+        <v>0</v>
+      </c>
+      <c r="P336" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>37</v>
+      </c>
+      <c r="R336" t="n">
+        <v>0</v>
+      </c>
+      <c r="S336" t="n">
+        <v>162</v>
+      </c>
+      <c r="T336" t="n">
+        <v>0</v>
+      </c>
+      <c r="U336" t="n">
+        <v>162</v>
+      </c>
+      <c r="V336" t="n">
+        <v>0</v>
+      </c>
+      <c r="W336" t="n">
+        <v>162</v>
+      </c>
+      <c r="X336" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>162</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y336"/>
+  <dimension ref="A1:Y337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27008,6 +27008,85 @@
         <v>162</v>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>100</v>
+      </c>
+      <c r="C337" t="n">
+        <v>116</v>
+      </c>
+      <c r="D337" t="n">
+        <v>50</v>
+      </c>
+      <c r="E337" t="n">
+        <v>116</v>
+      </c>
+      <c r="F337" t="n">
+        <v>0</v>
+      </c>
+      <c r="G337" t="n">
+        <v>194</v>
+      </c>
+      <c r="H337" t="n">
+        <v>0</v>
+      </c>
+      <c r="I337" t="n">
+        <v>194</v>
+      </c>
+      <c r="J337" t="n">
+        <v>0</v>
+      </c>
+      <c r="K337" t="n">
+        <v>194</v>
+      </c>
+      <c r="L337" t="n">
+        <v>0</v>
+      </c>
+      <c r="M337" t="n">
+        <v>194</v>
+      </c>
+      <c r="N337" t="n">
+        <v>0</v>
+      </c>
+      <c r="O337" t="n">
+        <v>0</v>
+      </c>
+      <c r="P337" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>42</v>
+      </c>
+      <c r="R337" t="n">
+        <v>0</v>
+      </c>
+      <c r="S337" t="n">
+        <v>206</v>
+      </c>
+      <c r="T337" t="n">
+        <v>0</v>
+      </c>
+      <c r="U337" t="n">
+        <v>206</v>
+      </c>
+      <c r="V337" t="n">
+        <v>0</v>
+      </c>
+      <c r="W337" t="n">
+        <v>206</v>
+      </c>
+      <c r="X337" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>206</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fractal_scape_refine_data.xlsx
+++ b/data/fractal_scape_refine_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y337"/>
+  <dimension ref="A1:Y338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27087,6 +27087,85 @@
         <v>206</v>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>0</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0</v>
+      </c>
+      <c r="D338" t="n">
+        <v>50</v>
+      </c>
+      <c r="E338" t="n">
+        <v>118</v>
+      </c>
+      <c r="F338" t="n">
+        <v>0</v>
+      </c>
+      <c r="G338" t="n">
+        <v>220</v>
+      </c>
+      <c r="H338" t="n">
+        <v>0</v>
+      </c>
+      <c r="I338" t="n">
+        <v>220</v>
+      </c>
+      <c r="J338" t="n">
+        <v>0</v>
+      </c>
+      <c r="K338" t="n">
+        <v>220</v>
+      </c>
+      <c r="L338" t="n">
+        <v>0</v>
+      </c>
+      <c r="M338" t="n">
+        <v>220</v>
+      </c>
+      <c r="N338" t="n">
+        <v>0</v>
+      </c>
+      <c r="O338" t="n">
+        <v>0</v>
+      </c>
+      <c r="P338" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>30</v>
+      </c>
+      <c r="R338" t="n">
+        <v>0</v>
+      </c>
+      <c r="S338" t="n">
+        <v>228</v>
+      </c>
+      <c r="T338" t="n">
+        <v>0</v>
+      </c>
+      <c r="U338" t="n">
+        <v>228</v>
+      </c>
+      <c r="V338" t="n">
+        <v>0</v>
+      </c>
+      <c r="W338" t="n">
+        <v>228</v>
+      </c>
+      <c r="X338" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
